--- a/terminology/CodeSystem-dlp-lecivelatky.xlsx
+++ b/terminology/CodeSystem-dlp-lecivelatky.xlsx
@@ -35,7 +35,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -47,7 +47,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Codesystem of DLP Lecive latky</t>
+    <t>DLP Lecive latky</t>
   </si>
   <si>
     <t>Status</t>
@@ -89,7 +89,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codesystem of DLP Lecive latky. Identification ingredient.</t>
+    <t>DLP Lecive latky - Czech national code system for active drug substances.</t>
   </si>
   <si>
     <t>Purpose</t>
